--- a/analyst/Ines/rmonize/data_proc_elem/DPE_IDEFICS_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_IDEFICS_INES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C99011-3A3F-48DE-B499-0CAFAE4AC7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2700B1E8-34B6-41DF-99F8-A63675B7564F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="119">
   <si>
     <t>index</t>
   </si>
@@ -156,13 +156,7 @@
     <t>BODY_FAT_FUP</t>
   </si>
   <si>
-    <t>Body fat precent at follow-up [%]</t>
-  </si>
-  <si>
     <t>BODY_FAT</t>
-  </si>
-  <si>
-    <t>Body fat precent at baseline  [%]</t>
   </si>
   <si>
     <t>AGE_ANTH_FUP</t>
@@ -390,6 +384,15 @@
   </si>
   <si>
     <t>hdl/38.67</t>
+  </si>
+  <si>
+    <t>To be generated by the DHO</t>
+  </si>
+  <si>
+    <t>Body fat percent at follow-up [%]</t>
+  </si>
+  <si>
+    <t>Body fat percent at baseline  [%]</t>
   </si>
 </sst>
 </file>
@@ -448,6 +451,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -494,7 +498,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -510,9 +514,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -550,9 +554,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -585,9 +589,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -620,9 +641,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -797,15 +835,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="67.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.7109375" customWidth="1"/>
     <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -854,23 +895,23 @@
         <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="H2" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -884,23 +925,23 @@
         <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="H3" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -914,23 +955,23 @@
         <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="H4" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -944,23 +985,23 @@
         <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="H5" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -974,23 +1015,23 @@
         <v>13</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1004,57 +1045,87 @@
         <v>13</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+      <c r="D8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>92</v>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1068,23 +1139,23 @@
         <v>13</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1098,23 +1169,23 @@
         <v>13</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1128,23 +1199,23 @@
         <v>13</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1158,21 +1229,21 @@
         <v>13</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1186,21 +1257,21 @@
         <v>13</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1214,81 +1285,117 @@
         <v>13</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>80</v>
+      <c r="C17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="2:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -1302,507 +1409,507 @@
         <v>13</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="2:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="2:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="2:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/analyst/Ines/rmonize/data_proc_elem/DPE_IDEFICS_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_IDEFICS_INES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2700B1E8-34B6-41DF-99F8-A63675B7564F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8F1AEE-8485-4010-A04D-1A86776DEB42}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="108">
   <si>
     <t>index</t>
   </si>
@@ -297,9 +297,6 @@
     <t>bmi_T3</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>waist_T3</t>
   </si>
   <si>
@@ -318,56 +315,6 @@
     <t>age_T3</t>
   </si>
   <si>
-    <t>gluc (foodcoll_calc_alldays_bls)</t>
-  </si>
-  <si>
-    <t>fruc (foodcoll_calc_alldays_bls)</t>
-  </si>
-  <si>
-    <t>energy_kcal (foodcoll_calc_alldays_bls)
-energy_kcal_day (Core)</t>
-  </si>
-  <si>
-    <t>carb (foodcoll_calc_alldays_bls)
-carb_day (Core)</t>
-  </si>
-  <si>
-    <t>protein (foodcoll_calc_alldays_bls)
-protein_day (Core)</t>
-  </si>
-  <si>
-    <t>fat (foodcoll_calc_alldays_bls)
-fat_day (Core)</t>
-  </si>
-  <si>
-    <t>alcohol (foodcoll_calc_alldays_bls)
-alcohol_day (Core)</t>
-  </si>
-  <si>
-    <t>fiber (foodcoll_calc_alldays_bls)
-fiber_day (Core)</t>
-  </si>
-  <si>
-    <t>sfa (foodcoll_calc_alldays_bls)
-sfa_day (Core)</t>
-  </si>
-  <si>
-    <t>mufa (foodcoll_calc_alldays_bls)
-mufa_day (Core)</t>
-  </si>
-  <si>
-    <t>pufa (foodcoll_calc_alldays_bls)
-pufa_day (Core)</t>
-  </si>
-  <si>
-    <t>sugars (foodcoll_calc_alldays_bls)
-sugars_day (Core)</t>
-  </si>
-  <si>
-    <t>na (foodcoll_calc_alldays_bls)
-na_day (Core)</t>
-  </si>
-  <si>
     <t>Sodium intake [mg/d]</t>
   </si>
   <si>
@@ -393,13 +340,22 @@
   </si>
   <si>
     <t>Body fat percent at baseline  [%]</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NA/K</t>
+  </si>
+  <si>
+    <t>NA;K</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -440,19 +396,12 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -475,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -489,13 +438,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -903,8 +849,8 @@
       <c r="G2" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>112</v>
+      <c r="H2" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="3" t="s">
@@ -933,8 +879,8 @@
       <c r="G3" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>113</v>
+      <c r="H3" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="3" t="s">
@@ -963,8 +909,8 @@
       <c r="G4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>114</v>
+      <c r="H4" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="3" t="s">
@@ -993,8 +939,8 @@
       <c r="G5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>115</v>
+      <c r="H5" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="3" t="s">
@@ -1087,7 +1033,7 @@
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>81</v>
@@ -1119,7 +1065,7 @@
         <v>87</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>81</v>
@@ -1142,7 +1088,7 @@
         <v>78</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>87</v>
@@ -1172,7 +1118,7 @@
         <v>78</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>87</v>
@@ -1202,7 +1148,7 @@
         <v>78</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>87</v>
@@ -1233,17 +1179,17 @@
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1261,17 +1207,17 @@
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1309,7 +1255,7 @@
         <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>13</v>
@@ -1327,7 +1273,7 @@
         <v>87</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>81</v>
@@ -1341,7 +1287,7 @@
         <v>43</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>13</v>
@@ -1359,7 +1305,7 @@
         <v>87</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>81</v>
@@ -1382,7 +1328,7 @@
         <v>78</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>87</v>
@@ -1398,518 +1344,536 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="2:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
+    <row r="19" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+      <c r="D19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
+      <c r="D20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
+      <c r="D21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
+      <c r="D22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
+      <c r="D23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
+      <c r="D24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" s="8" t="s">
+      <c r="D25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B30" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F35" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" s="8" t="s">
+      <c r="G35" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B35" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>90</v>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/analyst/Ines/rmonize/data_proc_elem/DPE_IDEFICS_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_IDEFICS_INES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8F1AEE-8485-4010-A04D-1A86776DEB42}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887AF4F2-3049-4523-B0B9-4AB76321F1BC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="108">
   <si>
     <t>index</t>
   </si>
@@ -345,17 +345,17 @@
     <t>NA</t>
   </si>
   <si>
+    <t>NA;K</t>
+  </si>
+  <si>
     <t>NA/K</t>
-  </si>
-  <si>
-    <t>NA;K</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,11 +398,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -439,7 +434,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1336,7 +1331,7 @@
       <c r="H18" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="I18" s="2"/>
+      <c r="I18" s="3"/>
       <c r="J18" s="2" t="s">
         <v>81</v>
       </c>
@@ -1366,7 +1361,9 @@
       <c r="H19" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I19" s="3"/>
+      <c r="I19" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J19" s="3" t="s">
         <v>81</v>
       </c>
@@ -1396,7 +1393,9 @@
       <c r="H20" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I20" s="3"/>
+      <c r="I20" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J20" s="3" t="s">
         <v>81</v>
       </c>
@@ -1426,7 +1425,9 @@
       <c r="H21" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I21" s="3"/>
+      <c r="I21" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J21" s="3" t="s">
         <v>81</v>
       </c>
@@ -1456,7 +1457,9 @@
       <c r="H22" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J22" s="3" t="s">
         <v>81</v>
       </c>
@@ -1486,7 +1489,9 @@
       <c r="H23" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I23" s="3"/>
+      <c r="I23" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J23" s="3" t="s">
         <v>81</v>
       </c>
@@ -1516,7 +1521,9 @@
       <c r="H24" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I24" s="3"/>
+      <c r="I24" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J24" s="3" t="s">
         <v>81</v>
       </c>
@@ -1546,7 +1553,9 @@
       <c r="H25" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I25" s="3"/>
+      <c r="I25" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J25" s="3" t="s">
         <v>81</v>
       </c>
@@ -1576,7 +1585,9 @@
       <c r="H26" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I26" s="3"/>
+      <c r="I26" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J26" s="3" t="s">
         <v>81</v>
       </c>
@@ -1606,7 +1617,9 @@
       <c r="H27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I27" s="3"/>
+      <c r="I27" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J27" s="3" t="s">
         <v>81</v>
       </c>
@@ -1636,7 +1649,9 @@
       <c r="H28" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I28" s="3"/>
+      <c r="I28" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J28" s="3" t="s">
         <v>81</v>
       </c>
@@ -1664,7 +1679,9 @@
       <c r="H29" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I29" s="3"/>
+      <c r="I29" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J29" s="3" t="s">
         <v>93</v>
       </c>
@@ -1692,7 +1709,9 @@
       <c r="H30" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I30" s="3"/>
+      <c r="I30" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J30" s="3" t="s">
         <v>93</v>
       </c>
@@ -1722,7 +1741,9 @@
       <c r="H31" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I31" s="3"/>
+      <c r="I31" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J31" s="3" t="s">
         <v>81</v>
       </c>
@@ -1752,7 +1773,9 @@
       <c r="H32" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="3"/>
+      <c r="I32" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J32" s="3" t="s">
         <v>81</v>
       </c>
@@ -1780,7 +1803,9 @@
       <c r="H33" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I33" s="3"/>
+      <c r="I33" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J33" s="3" t="s">
         <v>93</v>
       </c>
@@ -1808,7 +1833,9 @@
       <c r="H34" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I34" s="3"/>
+      <c r="I34" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J34" s="3" t="s">
         <v>93</v>
       </c>
@@ -1838,7 +1865,9 @@
       <c r="H35" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I35" s="3"/>
+      <c r="I35" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J35" s="3" t="s">
         <v>81</v>
       </c>
@@ -1860,15 +1889,17 @@
         <v>78</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>80</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="I36" s="3"/>
+        <v>107</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="J36" s="3" t="s">
         <v>81</v>
       </c>

--- a/analyst/Ines/rmonize/data_proc_elem/DPE_IDEFICS_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_IDEFICS_INES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887AF4F2-3049-4523-B0B9-4AB76321F1BC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D5CED8-92BB-4D67-9A7B-5A18BA8A56B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/analyst/Ines/rmonize/data_proc_elem/DPE_IDEFICS_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_IDEFICS_INES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D5CED8-92BB-4D67-9A7B-5A18BA8A56B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B208F45E-62B1-4B0F-9257-B428BF3C863B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="113">
   <si>
     <t>index</t>
   </si>
@@ -348,7 +348,22 @@
     <t>NA;K</t>
   </si>
   <si>
-    <t>NA/K</t>
+    <t>FFM;weight;height</t>
+  </si>
+  <si>
+    <t>(weight-FFM)/((height/100)^2)</t>
+  </si>
+  <si>
+    <t>body_fat_T3</t>
+  </si>
+  <si>
+    <t>bodyfat</t>
+  </si>
+  <si>
+    <t>`NA`/K</t>
+  </si>
+  <si>
+    <t>FMI_T3</t>
   </si>
 </sst>
 </file>
@@ -439,7 +454,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -455,9 +470,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -495,9 +510,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -530,26 +545,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -582,26 +580,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -776,7 +757,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="67.5703125" bestFit="1" customWidth="1"/>
@@ -1200,19 +1181,21 @@
       <c r="E14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>93</v>
+      <c r="F14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
+        <v>87</v>
       </c>
       <c r="I14" s="2"/>
-      <c r="J14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>94</v>
+      <c r="J14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1228,21 +1211,21 @@
       <c r="E15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>87</v>
+      <c r="F15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" t="s">
+        <v>108</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>88</v>
+      <c r="K15" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1258,17 +1241,14 @@
       <c r="E16" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>102</v>
+      <c r="F16" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" t="s">
+        <v>87</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>81</v>
@@ -1290,17 +1270,14 @@
       <c r="E17" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>102</v>
+      <c r="F17" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" t="s">
+        <v>87</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>81</v>
@@ -1679,9 +1656,7 @@
       <c r="H29" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>102</v>
-      </c>
+      <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
         <v>93</v>
       </c>
@@ -1709,9 +1684,7 @@
       <c r="H30" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>102</v>
-      </c>
+      <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
         <v>93</v>
       </c>
@@ -1803,9 +1776,7 @@
       <c r="H33" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>102</v>
-      </c>
+      <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
         <v>93</v>
       </c>
@@ -1833,9 +1804,7 @@
       <c r="H34" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>102</v>
-      </c>
+      <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
         <v>93</v>
       </c>
@@ -1865,9 +1834,7 @@
       <c r="H35" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>102</v>
-      </c>
+      <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
         <v>81</v>
       </c>
@@ -1895,11 +1862,9 @@
         <v>80</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>102</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
         <v>81</v>
       </c>
